--- a/DesignData/Excel_Masters/Unit/CharacterStats_Master.xlsx
+++ b/DesignData/Excel_Masters/Unit/CharacterStats_Master.xlsx
@@ -1279,7 +1279,7 @@
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2" t="s">
         <v>18</v>
@@ -1329,7 +1329,7 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H3" t="s">
         <v>21</v>
@@ -1379,7 +1379,7 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H4" t="s">
         <v>24</v>
@@ -1429,7 +1429,7 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H5" t="s">
         <v>27</v>
@@ -1479,7 +1479,7 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H6" t="s">
         <v>30</v>
@@ -1529,7 +1529,7 @@
         <v>1</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H7" t="s">
         <v>32</v>
@@ -1579,7 +1579,7 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H8" t="s">
         <v>34</v>
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H9" t="s">
         <v>36</v>
@@ -1679,7 +1679,7 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H10" t="s">
         <v>38</v>
@@ -1729,7 +1729,7 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H11" t="s">
         <v>40</v>
@@ -1779,7 +1779,7 @@
         <v>1</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H12" t="s">
         <v>42</v>
@@ -1829,7 +1829,7 @@
         <v>1</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H13" t="s">
         <v>44</v>
@@ -1879,7 +1879,7 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H14" t="s">
         <v>46</v>
@@ -1929,7 +1929,7 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H15" t="s">
         <v>48</v>
@@ -1979,7 +1979,7 @@
         <v>1</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H16" t="s">
         <v>50</v>
@@ -2029,7 +2029,7 @@
         <v>1</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H17" t="s">
         <v>52</v>
@@ -2079,7 +2079,7 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H18" t="s">
         <v>54</v>
@@ -2129,7 +2129,7 @@
         <v>1</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H19" t="s">
         <v>56</v>
@@ -2179,7 +2179,7 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H20" t="s">
         <v>58</v>
@@ -2229,7 +2229,7 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H21" t="s">
         <v>60</v>
@@ -2279,7 +2279,7 @@
         <v>1</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H22" t="s">
         <v>62</v>
@@ -2329,7 +2329,7 @@
         <v>1</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H23" t="s">
         <v>64</v>
@@ -2379,7 +2379,7 @@
         <v>1</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H24" t="s">
         <v>66</v>
@@ -2412,5 +2412,6 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>